--- a/code/SMR_inputs.xlsx
+++ b/code/SMR_inputs.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mgarrous/Documents/SMR_deployment/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23C8E52-61B4-9C40-9A1F-D7F2E25CDDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001F74EF-2A41-224C-AA13-FC462F02B816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2160" yWindow="1440" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FOAK_act" sheetId="3" r:id="rId1"/>
+    <sheet name="FOAK" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/code/SMR_inputs.xlsx
+++ b/code/SMR_inputs.xlsx
@@ -1,122 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10209"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mgarrous/Documents/SMR_deployment/code/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001F74EF-2A41-224C-AA13-FC462F02B816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="1440" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2160" yWindow="1440" windowWidth="29040" windowHeight="17640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FOAK" sheetId="3" r:id="rId1"/>
+    <sheet name="FOAK" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NOAK_with_inc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NOAK_wo_inc" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Power in MWe</t>
-  </si>
-  <si>
-    <t>Power in MWt</t>
-  </si>
-  <si>
-    <t>Thermal Efficiency</t>
-  </si>
-  <si>
-    <t>Thermal transfer efficiency</t>
-  </si>
-  <si>
-    <t>Outlet Temp (C)</t>
-  </si>
-  <si>
-    <t>CAPEX $/MWe</t>
-  </si>
-  <si>
-    <t>FOPEX $/MWe-y</t>
-  </si>
-  <si>
-    <t>VOM in $/MWh-e</t>
-  </si>
-  <si>
-    <t>PWR</t>
-  </si>
-  <si>
-    <t>MSR</t>
-  </si>
-  <si>
-    <t>Life (y)</t>
-  </si>
-  <si>
-    <t>HTR</t>
-  </si>
-  <si>
-    <t>MR</t>
-  </si>
-  <si>
-    <t>SFR</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -131,49 +67,117 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,213 +465,694 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8178B4E1-4235-A940-9555-1BFA1F4EA201}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col width="14.83203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="13.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="4">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Power in MWe</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Power in MWt</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Thermal Efficiency</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Thermal transfer efficiency</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Outlet Temp (C)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX $/MWe</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>FOPEX $/MWe-y</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>VOM in $/MWh-e</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Life (y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="4" t="n">
         <v>250</v>
       </c>
       <c r="D2" s="3">
         <f>B2/C2</f>
-        <v>0.308</v>
-      </c>
-      <c r="E2" s="4">
+        <v/>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="4" t="n">
         <v>316</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="4" t="n">
         <v>22561</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="5" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D3" s="3">
+        <f>B3/C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>850</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10166</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="D4" s="3">
+        <f>B4/C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7312</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B3" s="4">
-        <v>265</v>
-      </c>
-      <c r="C3" s="4">
-        <v>500</v>
-      </c>
-      <c r="D3" s="3">
-        <f t="shared" ref="D3:D6" si="0">B3/C3</f>
-        <v>0.53</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="F3" s="4">
-        <v>850</v>
-      </c>
-      <c r="G3">
-        <v>10166</v>
-      </c>
-      <c r="H3" s="5">
-        <v>104</v>
-      </c>
-      <c r="I3" s="9">
-        <v>19.3</v>
-      </c>
-      <c r="J3" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4">
-        <v>195</v>
-      </c>
-      <c r="C4" s="4">
-        <v>440</v>
-      </c>
-      <c r="D4" s="3">
-        <f t="shared" si="0"/>
-        <v>0.44318181818181818</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="D5" s="3">
+        <f>B5/C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>700</v>
       </c>
-      <c r="G4">
-        <v>7312</v>
-      </c>
-      <c r="H4" s="5">
-        <v>181</v>
-      </c>
-      <c r="I4" s="9">
-        <v>8.9</v>
-      </c>
-      <c r="J4" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="C5" s="4">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3">
-        <f t="shared" si="0"/>
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="F5" s="4">
-        <v>700</v>
-      </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>18115</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="5" t="n">
         <v>131</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="5" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="4">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SFR</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="4" t="n">
         <v>286</v>
       </c>
       <c r="D6" s="3">
-        <f t="shared" si="0"/>
-        <v>0.34965034965034963</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="F6" s="4">
+        <f>B6/C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>510</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>22154</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="5" t="n">
         <v>131</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="5" t="n">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Power in MWe</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Power in MWt</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Thermal Efficiency</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Thermal transfer efficiency</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Outlet Temp (C)</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>CAPEX $/MWe</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>FOPEX $/MWe-y</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>VOM in $/MWh-e</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Life (y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>77</v>
+      </c>
+      <c r="C2" t="n">
+        <v>250</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>316</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22561</v>
+      </c>
+      <c r="H2" t="n">
+        <v>180</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="F3" t="n">
+        <v>850</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8482.690925318901</v>
+      </c>
+      <c r="H3" t="n">
+        <v>104</v>
+      </c>
+      <c r="I3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>195</v>
+      </c>
+      <c r="C4" t="n">
+        <v>440</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>700</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6101.262644691305</v>
+      </c>
+      <c r="H4" t="n">
+        <v>181</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>700</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18115</v>
+      </c>
+      <c r="H5" t="n">
+        <v>131</v>
+      </c>
+      <c r="I5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SFR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>286</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>510</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22154</v>
+      </c>
+      <c r="H6" t="n">
+        <v>131</v>
+      </c>
+      <c r="I6" t="n">
+        <v>78</v>
+      </c>
+      <c r="J6" t="n">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Power in MWe</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Power in MWt</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Thermal Efficiency</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Thermal transfer efficiency</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Outlet Temp (C)</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>CAPEX $/MWe</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>FOPEX $/MWe-y</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>VOM in $/MWh-e</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Life (y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>77</v>
+      </c>
+      <c r="C2" t="n">
+        <v>250</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>316</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22561</v>
+      </c>
+      <c r="H2" t="n">
+        <v>180</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="F3" t="n">
+        <v>850</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8482.690925318901</v>
+      </c>
+      <c r="H3" t="n">
+        <v>104</v>
+      </c>
+      <c r="I3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>195</v>
+      </c>
+      <c r="C4" t="n">
+        <v>440</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>700</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6101.262644691305</v>
+      </c>
+      <c r="H4" t="n">
+        <v>181</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>700</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18115</v>
+      </c>
+      <c r="H5" t="n">
+        <v>131</v>
+      </c>
+      <c r="I5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SFR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>286</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>510</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22154</v>
+      </c>
+      <c r="H6" t="n">
+        <v>131</v>
+      </c>
+      <c r="I6" t="n">
+        <v>78</v>
+      </c>
+      <c r="J6" t="n">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/code/SMR_inputs.xlsx
+++ b/code/SMR_inputs.xlsx
@@ -1,130 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mgarrous/Documents/SMR_deployment/code/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852A9983-D97C-1740-8BFF-D4D9D4B2B1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="2420" windowWidth="14680" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="860" yWindow="2420" windowWidth="14680" windowHeight="17640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FOAK" sheetId="1" r:id="rId1"/>
-    <sheet name="NOAK_with_inc" sheetId="2" r:id="rId2"/>
-    <sheet name="NOAK_wo_inc" sheetId="3" r:id="rId3"/>
+    <sheet name="FOAK" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NOAK_with_inc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NOAK_wo_inc" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="15">
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Power in MWe</t>
-  </si>
-  <si>
-    <t>Power in MWt</t>
-  </si>
-  <si>
-    <t>Thermal Efficiency</t>
-  </si>
-  <si>
-    <t>Thermal transfer efficiency</t>
-  </si>
-  <si>
-    <t>Outlet Temp (C)</t>
-  </si>
-  <si>
-    <t>CAPEX $/MWe</t>
-  </si>
-  <si>
-    <t>FOPEX $/MWe-y</t>
-  </si>
-  <si>
-    <t>VOM in $/MWh-e</t>
-  </si>
-  <si>
-    <t>Life (y)</t>
-  </si>
-  <si>
-    <t>PWR</t>
-  </si>
-  <si>
-    <t>HTR</t>
-  </si>
-  <si>
-    <t>MSR</t>
-  </si>
-  <si>
-    <t>MR</t>
-  </si>
-  <si>
-    <t>SFR</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -154,52 +88,120 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -487,209 +489,243 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col width="14.83203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="13.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Power in MWe</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Power in MWt</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Thermal Efficiency</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Thermal transfer efficiency</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Outlet Temp (C)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX $/MWe</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>FOPEX $/MWe-y</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>VOM in $/MWh-e</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Life (y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="4" t="n">
         <v>250</v>
       </c>
       <c r="D2" s="3">
         <f>B2/C2</f>
-        <v>0.308</v>
-      </c>
-      <c r="E2" s="4">
+        <v/>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="4" t="n">
         <v>316</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="4" t="n">
         <v>22561000</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="5" t="n">
         <v>180000</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="5" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="4">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>265</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="4" t="n">
         <v>500</v>
       </c>
       <c r="D3" s="3">
         <f>B3/C3</f>
-        <v>0.53</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="F3" s="4">
+        <v/>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>850</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>10166000</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="5" t="n">
         <v>104000</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="5" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>195</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="4" t="n">
         <v>440</v>
       </c>
       <c r="D4" s="3">
         <f>B4/C4</f>
-        <v>0.44318181818181818</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="F4" s="4">
+        <v/>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>700</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>7312000</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="5" t="n">
         <v>181000</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="9" t="n">
         <v>8.9</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="5" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="8">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
         <v>3.5</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="D5" s="3">
         <f>B5/C5</f>
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E5" s="3">
+        <v/>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="4" t="n">
         <v>700</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>18115000</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="5" t="n">
         <v>131000</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="5" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="4">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SFR</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="4" t="n">
         <v>286</v>
       </c>
       <c r="D6" s="3">
         <f>B6/C6</f>
-        <v>0.34965034965034963</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="F6" s="4">
+        <v/>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>510</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>22154000</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="5" t="n">
         <v>131000</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="5" t="n">
         <v>60</v>
       </c>
     </row>
@@ -699,184 +735,218 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Power in MWe</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Power in MWt</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Thermal Efficiency</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Thermal transfer efficiency</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Outlet Temp (C)</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>CAPEX $/MWe</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>FOPEX $/MWe-y</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>VOM in $/MWh-e</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>Life (y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>77</v>
+      </c>
+      <c r="C2" t="n">
+        <v>250</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2">
-        <v>77</v>
-      </c>
-      <c r="C2">
-        <v>250</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>316</v>
       </c>
-      <c r="G2">
-        <v>22561</v>
-      </c>
-      <c r="H2">
-        <v>180</v>
-      </c>
-      <c r="I2">
+      <c r="G2" t="n">
+        <v>20981730</v>
+      </c>
+      <c r="H2" t="n">
+        <v>180000</v>
+      </c>
+      <c r="I2" t="n">
         <v>7.2</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>265</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>500</v>
       </c>
-      <c r="E3">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="F3">
+      <c r="E3" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="F3" t="n">
         <v>850</v>
       </c>
-      <c r="G3">
-        <v>8589.5374621698229</v>
-      </c>
-      <c r="H3">
-        <v>104</v>
-      </c>
-      <c r="I3">
+      <c r="G3" t="n">
+        <v>9454380</v>
+      </c>
+      <c r="H3" t="n">
+        <v>104000</v>
+      </c>
+      <c r="I3" t="n">
         <v>19.3</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>195</v>
+      </c>
+      <c r="C4" t="n">
+        <v>440</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>700</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5964260.90400195</v>
+      </c>
+      <c r="H4" t="n">
+        <v>181000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C5" t="n">
         <v>12</v>
       </c>
-      <c r="B4">
-        <v>195</v>
-      </c>
-      <c r="C4">
-        <v>440</v>
-      </c>
-      <c r="E4">
-        <v>0.94</v>
-      </c>
-      <c r="F4">
+      <c r="E5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F5" t="n">
         <v>700</v>
       </c>
-      <c r="G4">
-        <v>6178.1131146356229</v>
-      </c>
-      <c r="H4">
-        <v>181</v>
-      </c>
-      <c r="I4">
-        <v>8.9</v>
-      </c>
-      <c r="J4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>0.9</v>
-      </c>
-      <c r="F5">
-        <v>700</v>
-      </c>
-      <c r="G5">
-        <v>18115</v>
-      </c>
-      <c r="H5">
-        <v>131</v>
-      </c>
-      <c r="I5">
+      <c r="G5" t="n">
+        <v>14776064.86269083</v>
+      </c>
+      <c r="H5" t="n">
+        <v>131000</v>
+      </c>
+      <c r="I5" t="n">
         <v>29.6</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>SFR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>100</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>286</v>
       </c>
-      <c r="E6">
-        <v>0.94</v>
-      </c>
-      <c r="F6">
+      <c r="E6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F6" t="n">
         <v>510</v>
       </c>
-      <c r="G6">
-        <v>22154</v>
-      </c>
-      <c r="H6">
-        <v>131</v>
-      </c>
-      <c r="I6">
+      <c r="G6" t="n">
+        <v>22154000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>131000</v>
+      </c>
+      <c r="I6" t="n">
         <v>78</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>60</v>
       </c>
     </row>
@@ -886,194 +956,227 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Power in MWe</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Power in MWt</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Thermal Efficiency</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Thermal transfer efficiency</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Outlet Temp (C)</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>CAPEX $/MWe</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>FOPEX $/MWe-y</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>VOM in $/MWh-e</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>Life (y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>77</v>
+      </c>
+      <c r="C2" t="n">
+        <v>250</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2">
-        <v>77</v>
-      </c>
-      <c r="C2">
-        <v>250</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>316</v>
       </c>
-      <c r="G2">
-        <v>22561</v>
-      </c>
-      <c r="H2">
-        <v>180</v>
-      </c>
-      <c r="I2">
+      <c r="G2" t="n">
+        <v>22561000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>180000</v>
+      </c>
+      <c r="I2" t="n">
         <v>7.2</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>HTR</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>265</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>500</v>
       </c>
-      <c r="E3">
-        <v>0.89700000000000002</v>
-      </c>
-      <c r="F3">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="F3" t="n">
         <v>850</v>
       </c>
-      <c r="G3">
-        <v>8589.5374621698229</v>
-      </c>
-      <c r="H3">
-        <v>104</v>
-      </c>
-      <c r="I3">
+      <c r="G3" t="n">
+        <v>10166000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>104000</v>
+      </c>
+      <c r="I3" t="n">
         <v>19.3</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>195</v>
+      </c>
+      <c r="C4" t="n">
+        <v>440</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>700</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7312000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>181000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C5" t="n">
         <v>12</v>
       </c>
-      <c r="B4">
-        <v>195</v>
-      </c>
-      <c r="C4">
-        <v>440</v>
-      </c>
-      <c r="E4">
-        <v>0.94</v>
-      </c>
-      <c r="F4">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F5" t="n">
         <v>700</v>
       </c>
-      <c r="G4">
-        <v>6178.1131146356229</v>
-      </c>
-      <c r="H4">
-        <v>181</v>
-      </c>
-      <c r="I4">
-        <v>8.9</v>
-      </c>
-      <c r="J4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>0.9</v>
-      </c>
-      <c r="F5">
-        <v>700</v>
-      </c>
-      <c r="G5">
-        <v>18115</v>
-      </c>
-      <c r="H5">
-        <v>131</v>
-      </c>
-      <c r="I5">
+      <c r="G5" t="n">
+        <v>18115000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>131000</v>
+      </c>
+      <c r="I5" t="n">
         <v>29.6</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>SFR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>100</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>286</v>
       </c>
-      <c r="E6">
-        <v>0.94</v>
-      </c>
-      <c r="F6">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F6" t="n">
         <v>510</v>
       </c>
-      <c r="G6">
-        <v>22154</v>
-      </c>
-      <c r="H6">
-        <v>131</v>
-      </c>
-      <c r="I6">
+      <c r="G6" t="n">
+        <v>22154000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>131000</v>
+      </c>
+      <c r="I6" t="n">
         <v>78</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>